--- a/bit/美客多声誉/武汉泽顺店铺声誉信息汇总2026-04-19-00.xlsx
+++ b/bit/美客多声誉/武汉泽顺店铺声誉信息汇总2026-04-19-00.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-19 00:45:03</t>
+          <t>2026-04-19 00:50:09</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-04-19 00:46:10</t>
+          <t>2026-04-19 00:51:02</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-19 00:46:57</t>
+          <t>2026-04-19 00:51:50</t>
         </is>
       </c>
     </row>
